--- a/artfynd/A 32355-2021 artfynd.xlsx
+++ b/artfynd/A 32355-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32355-2021 artfynd.xlsx
+++ b/artfynd/A 32355-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17225326</v>
+        <v>17225325</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sundtången  strax N om Kycklingvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457850.3200316892</v>
+        <v>457850</v>
       </c>
       <c r="R2" t="n">
-        <v>7165673.734308198</v>
+        <v>7165674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +746,14 @@
           <t>2014-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-06-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Artbestämd av Anders Nordin</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,6 +782,11 @@
       <c r="AO2" t="inlineStr">
         <is>
           <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Anders Nordin</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,15 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17225328</v>
+        <v>17225324</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,21 +819,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457816.7262899039</v>
+        <v>457930</v>
       </c>
       <c r="R3" t="n">
-        <v>7165730.431925772</v>
+        <v>7165825</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +876,9 @@
           <t>2014-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17225327</v>
+        <v>17225328</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -983,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457850.3200316892</v>
+        <v>457817</v>
       </c>
       <c r="R4" t="n">
-        <v>7165673.734308198</v>
+        <v>7165730</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,19 +995,9 @@
           <t>2014-06-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,37 +1046,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17225339</v>
+        <v>17225329</v>
       </c>
       <c r="B5" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1117,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457722.3788306011</v>
+        <v>457607</v>
       </c>
       <c r="R5" t="n">
-        <v>7165282.300128704</v>
+        <v>7165341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,22 +1111,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-06-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-06-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1211,15 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17225340</v>
+        <v>17225338</v>
       </c>
       <c r="B6" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457731.7153193107</v>
+        <v>457739</v>
       </c>
       <c r="R6" t="n">
-        <v>7165335.40293548</v>
+        <v>7165292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,19 +1233,9 @@
           <t>2014-06-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-06-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,37 +1284,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17225329</v>
+        <v>17225339</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1385,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457606.7083272438</v>
+        <v>457722</v>
       </c>
       <c r="R7" t="n">
-        <v>7165340.581453484</v>
+        <v>7165282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,22 +1349,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,37 +1403,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17225324</v>
+        <v>17225340</v>
       </c>
       <c r="B8" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1519,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457930.2017141375</v>
+        <v>457732</v>
       </c>
       <c r="R8" t="n">
-        <v>7165824.574476199</v>
+        <v>7165335</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,22 +1468,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1613,37 +1522,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17225338</v>
+        <v>17225326</v>
       </c>
       <c r="B9" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1653,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457739.282560766</v>
+        <v>457850</v>
       </c>
       <c r="R9" t="n">
-        <v>7165292.367839865</v>
+        <v>7165674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,22 +1587,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-06-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-06-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1740,154 +1634,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>17225325</v>
-      </c>
-      <c r="B10" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>498</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Liten sotlav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Acolium karelicum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Sundtången  strax N om Kycklingvattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>457850.3200316892</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7165673.734308198</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2014-06-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Artbestämd av Anders Nordin</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Anders Nordin</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
